--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484097_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484097_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6137</v>
+        <v>2.0676</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4805</v>
+        <v>4.2991</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8669</v>
+        <v>-2.2316</v>
       </c>
       <c r="G2" t="n">
         <v>3.1207</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8508</v>
+        <v>0.3047</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1359</v>
+        <v>-0.3173</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9867</v>
+        <v>0.6219</v>
       </c>
       <c r="V2" t="n">
         <v>-2.9449</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7199</v>
+        <v>1.0985</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1872</v>
+        <v>0.3041</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9071</v>
+        <v>0.7944</v>
       </c>
       <c r="G3" t="n">
-        <v>1.085</v>
+        <v>1.2197</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1237</v>
+        <v>-0.1509</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0388</v>
+        <v>1.3706</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2248</v>
+        <v>1.779</v>
       </c>
       <c r="K3" t="n">
-        <v>1.024</v>
+        <v>0.1623</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2008</v>
+        <v>1.6167</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1398</v>
+        <v>-0.5593</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0998</v>
+        <v>-0.3132</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2396</v>
+        <v>-0.2461</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1741</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3348</v>
+        <v>0.3245</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5557</v>
+        <v>-0.289</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7792</v>
+        <v>0.6135</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6888</v>
+        <v>0.5462</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5177</v>
+        <v>-0.2517</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2485</v>
+        <v>0.7945</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5178</v>
+        <v>-0.6918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7663</v>
+        <v>1.4863</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2197</v>
+        <v>1.085</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1509</v>
+        <v>1.1237</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3706</v>
+        <v>-0.0388</v>
       </c>
       <c r="J4" t="n">
-        <v>1.779</v>
+        <v>1.2248</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1623</v>
+        <v>1.024</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6167</v>
+        <v>0.2008</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5593</v>
+        <v>-0.1398</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3132</v>
+        <v>0.0998</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2461</v>
+        <v>-0.2396</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9919</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>-3.1741</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5255</v>
+        <v>0.4095</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1109</v>
+        <v>0.0511</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5854</v>
+        <v>0.3583</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5462</v>
+        <v>0.6888</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7979000000000001</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2517</v>
+        <v>-0.5177</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2408</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6736</v>
+        <v>-2.0161</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4328</v>
+        <v>1.9378</v>
       </c>
       <c r="G5" t="n">
         <v>0.7658</v>
@@ -844,13 +844,13 @@
         <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8819</v>
+        <v>0.2806</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7368</v>
+        <v>-0.0793</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1451</v>
+        <v>0.3598</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9262</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3965</v>
+        <v>-1.6791</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.4786</v>
+        <v>-3.677</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0821</v>
+        <v>1.998</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4578</v>
@@ -922,13 +922,13 @@
         <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.352</v>
+        <v>0.0694</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1872</v>
+        <v>-0.0112</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1648</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>1.4867</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4197</v>
+        <v>-1.7966</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3139</v>
+        <v>-3.4103</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8942</v>
+        <v>1.6136</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1291</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7708</v>
+        <v>0.3939</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0622</v>
+        <v>-0.1586</v>
       </c>
       <c r="U7" t="n">
-        <v>0.833</v>
+        <v>0.5525</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2517</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7898</v>
+        <v>-2.2352</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2873</v>
+        <v>-1.8168</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.4183</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2702</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3212</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8728</v>
+        <v>-0.4024</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4484</v>
+        <v>-0.3642</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.9965</v>
+        <v>-6.5622</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.3991</v>
+        <v>-6.4979</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5974</v>
+        <v>-0.0644</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7025</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.5637</v>
+        <v>-1.1294</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.9327</v>
+        <v>-1.0315</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.631</v>
+        <v>-0.0979</v>
       </c>
       <c r="V9" t="n">
         <v>-0.532</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.2612</v>
+        <v>-8.390799999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.377</v>
+        <v>-13.5067</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1157</v>
+        <v>5.1158</v>
       </c>
       <c r="G10" t="n">
         <v>-3.368399999999999</v>
@@ -1219,7 +1219,7 @@
         <v>-1.9779</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8126</v>
+        <v>-0.8126000000000002</v>
       </c>
       <c r="O10" t="n">
         <v>-1.1654</v>
@@ -1234,10 +1234,10 @@
         <v>10.9111</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9839</v>
+        <v>-0.1133999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.1084</v>
+        <v>-2.2382</v>
       </c>
       <c r="U10" t="n">
         <v>2.1246</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.6495</v>
+        <v>8.3637</v>
       </c>
       <c r="E11" t="n">
-        <v>5.0813</v>
+        <v>5.7955</v>
       </c>
       <c r="F11" t="n">
         <v>2.5682</v>
@@ -1312,10 +1312,10 @@
         <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5044999999999999</v>
+        <v>0.2097</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2979</v>
+        <v>-0.5837</v>
       </c>
       <c r="U11" t="n">
         <v>0.7934</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.8959</v>
+        <v>2.5005</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3119</v>
+        <v>0.4957</v>
       </c>
       <c r="F12" t="n">
-        <v>1.584</v>
+        <v>2.0049</v>
       </c>
       <c r="G12" t="n">
         <v>2.0206</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0061</v>
+        <v>0.6107</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0034</v>
+        <v>0.1872</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0027</v>
+        <v>0.4236</v>
       </c>
       <c r="V12" t="n">
         <v>0.266</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4909</v>
+        <v>2.4014</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-1.5688</v>
       </c>
       <c r="F13" t="n">
-        <v>3.065</v>
+        <v>3.9702</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3685</v>
+        <v>-0.7104</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8067</v>
+        <v>-2.8169</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1751</v>
+        <v>2.1065</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5394</v>
+        <v>-1.1722</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6197</v>
+        <v>-2.3069</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0803</v>
+        <v>1.1347</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9079</v>
+        <v>0.4618</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.187</v>
+        <v>-0.51</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0948</v>
+        <v>0.9718</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9919</v>
+        <v>2.579</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1903</v>
+        <v>2.579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5985</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3683</v>
+        <v>-0.3966</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9668</v>
+        <v>0.9294</v>
       </c>
       <c r="V13" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.153</v>
+        <v>2.1219</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4454</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7075</v>
+        <v>2.696</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5018</v>
+        <v>0.3685</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7233</v>
+        <v>-0.8067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2215</v>
+        <v>1.1751</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5397</v>
+        <v>-0.5394</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3791</v>
+        <v>-0.6197</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1606</v>
+        <v>0.0803</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0379</v>
+        <v>0.9079</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6558</v>
+        <v>-0.187</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3821</v>
+        <v>1.0948</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3139</v>
+        <v>0.2296</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6236</v>
+        <v>-0.3683</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6903</v>
+        <v>0.5979</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.266</v>
+        <v>0.532</v>
       </c>
       <c r="W14" t="n">
-        <v>0.266</v>
+        <v>0.532</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.745</v>
+        <v>1.5306</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.977</v>
+        <v>0.9353</v>
       </c>
       <c r="F15" t="n">
-        <v>3.722</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7104</v>
+        <v>1.5018</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.8169</v>
+        <v>1.7233</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1065</v>
+        <v>-0.2215</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1722</v>
+        <v>2.5397</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.3069</v>
+        <v>2.3791</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1347</v>
+        <v>0.1606</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4618</v>
+        <v>-1.0379</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.51</v>
+        <v>-0.6558</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9718</v>
+        <v>-0.3821</v>
       </c>
       <c r="P15" t="n">
-        <v>2.579</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>2.579</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1236</v>
+        <v>0.6915</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8047</v>
+        <v>0.1135</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6812</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1492</v>
+        <v>0.0429</v>
       </c>
       <c r="E16" t="n">
         <v>-2.6831</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5339</v>
+        <v>2.726</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3502</v>
@@ -1702,13 +1702,13 @@
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.212</v>
+        <v>-0.0198</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3683</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1563</v>
+        <v>0.3485</v>
       </c>
       <c r="V16" t="n">
         <v>1.2065</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.871</v>
+        <v>-1.8764</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5571</v>
+        <v>-2.2016</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3138</v>
+        <v>0.3252</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8798</v>
+        <v>-2.3016</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1584</v>
+        <v>-1.8247</v>
       </c>
       <c r="I17" t="n">
+        <v>-0.4768</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1.3146</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.5592</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.7554</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.9869</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1.2655</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.2786</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-2.186</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-1.5058</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.6802</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.3062</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.3474</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.9588</v>
       </c>
       <c r="P17" t="n">
         <v>0.7935</v>
@@ -1780,22 +1780,22 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3622</v>
+        <v>-0.0311</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5613</v>
+        <v>-0.3513</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.199</v>
+        <v>0.3202</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1469</v>
+        <v>-0.3373</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>-0.3373</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0742</v>
+        <v>-1.9824</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4514</v>
+        <v>-3.2473</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3771</v>
+        <v>1.2649</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8827</v>
@@ -1858,13 +1858,13 @@
         <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2766</v>
+        <v>0.3684</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6121</v>
+        <v>-0.408</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8887</v>
+        <v>0.7764</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6745</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5787</v>
+        <v>-2.1609</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7118</v>
+        <v>-2.0673</v>
       </c>
       <c r="F19" t="n">
-        <v>0.133</v>
+        <v>-0.0936</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3016</v>
+        <v>-0.8798</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8247</v>
+        <v>-1.1584</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4768</v>
+        <v>0.2786</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3146</v>
+        <v>-2.186</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5592</v>
+        <v>-1.5058</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7554</v>
+        <v>-0.6802</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9869</v>
+        <v>1.3062</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2655</v>
+        <v>0.3474</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2786</v>
+        <v>0.9588</v>
       </c>
       <c r="P19" t="n">
         <v>0.7935</v>
@@ -1936,22 +1936,22 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7334000000000001</v>
+        <v>0.0723</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8615</v>
+        <v>0.0511</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1281</v>
+        <v>0.0212</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3373</v>
+        <v>-2.1469</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3373</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>10.2612</v>
+        <v>10.9413</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.1159</v>
+        <v>-5.1157</v>
       </c>
       <c r="F20" t="n">
-        <v>15.3769</v>
+        <v>16.0571</v>
       </c>
       <c r="G20" t="n">
         <v>3.3684</v>
@@ -1990,7 +1990,7 @@
         <v>1.9781</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8126999999999996</v>
+        <v>0.8126999999999998</v>
       </c>
       <c r="L20" t="n">
         <v>1.1652</v>
@@ -2002,7 +2002,7 @@
         <v>-4.2138</v>
       </c>
       <c r="O20" t="n">
-        <v>5.6042</v>
+        <v>5.604200000000001</v>
       </c>
       <c r="P20" t="n">
         <v>2.9757</v>
@@ -2014,22 +2014,22 @@
         <v>13.8869</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9838</v>
+        <v>2.6641</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.1245</v>
+        <v>-2.1244</v>
       </c>
       <c r="U20" t="n">
-        <v>4.1085</v>
+        <v>4.7887</v>
       </c>
       <c r="V20" t="n">
-        <v>1.9332</v>
+        <v>1.933200000000001</v>
       </c>
       <c r="W20" t="n">
         <v>5.942100000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.0089</v>
+        <v>-4.008900000000001</v>
       </c>
     </row>
   </sheetData>
